--- a/output/ATI_buyout_recommendations_internal.xlsx
+++ b/output/ATI_buyout_recommendations_internal.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -78,12 +84,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F6FED"/>
+        <fgColor rgb="001F7A4D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F7A4D"/>
+        <fgColor rgb="002F6FED"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -176,8 +182,8 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -194,8 +200,17 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -203,8 +218,8 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +603,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата: 2026-07-30 12:36 | Критерий: ликвидность A/B или сильный C (спрос ≥2 или потенц. выручка ≥ $3 000)</t>
+          <t>Дата: 2026-07-30 12:45 | Критерий: ликвидность A/B или сильный C (спрос ≥2 или потенц. выручка ≥ $3 000)</t>
         </is>
       </c>
     </row>
@@ -810,12 +825,12 @@
       </c>
       <c r="I1" s="5" t="inlineStr">
         <is>
-          <t>Уверенность</t>
+          <t>Ликвидность</t>
         </is>
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Флаг цены</t>
+          <t>Уверенность в цене</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
@@ -864,12 +879,12 @@
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -916,14 +931,14 @@
       <c r="H3" s="15" t="n">
         <v>154500</v>
       </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
@@ -972,12 +987,12 @@
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -1024,14 +1039,14 @@
       <c r="H5" s="15" t="n">
         <v>100000</v>
       </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -1078,14 +1093,14 @@
       <c r="H6" s="9" t="n">
         <v>92400</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1132,14 +1147,14 @@
       <c r="H7" s="15" t="n">
         <v>86800</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -1188,12 +1203,12 @@
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J8" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -1242,12 +1257,12 @@
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -1296,12 +1311,12 @@
       </c>
       <c r="I10" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -1350,12 +1365,12 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
@@ -1404,12 +1419,12 @@
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J12" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J12" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -1456,14 +1471,14 @@
       <c r="H13" s="15" t="n">
         <v>61950</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
@@ -1512,12 +1527,12 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -1564,24 +1579,24 @@
       <c r="H15" s="15" t="n">
         <v>56700</v>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: ЮВТ, ТАУ Центр, Тулпар Техник, Ямал (5 уник.)</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, Руслайн, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
         </is>
       </c>
     </row>
@@ -1618,14 +1633,14 @@
       <c r="H16" s="9" t="n">
         <v>49200</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J16" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -1672,14 +1687,14 @@
       <c r="H17" s="15" t="n">
         <v>48000</v>
       </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -1726,14 +1741,14 @@
       <c r="H18" s="9" t="n">
         <v>47750</v>
       </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -1782,12 +1797,12 @@
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
@@ -1834,14 +1849,14 @@
       <c r="H20" s="9" t="n">
         <v>46000</v>
       </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -1890,12 +1905,12 @@
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -1944,12 +1959,12 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -1998,22 +2013,22 @@
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис (3 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Северсталь, Руслайн (2 уник.) | Запросы ТУЗ+EXP: 3 · клиенты: Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис (3 уник.)</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), Руслайн, Аллюр Сервис, qty≈121). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 2 — Северсталь, Руслайн, qty≈58); запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, АК Тулпар (Джет Экспресс), Аллюр Сервис, qty≈82.6667). Сопоставление: ALT P/N, точное P/N. На складе: 249 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $169.50: медиана продажных цен ТАЗ (все даты) (n=4, min $10.00, max $175.00, последний заказ 2025-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (356 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -2050,14 +2065,14 @@
       <c r="H24" s="9" t="n">
         <v>40800</v>
       </c>
-      <c r="I24" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I24" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -2106,12 +2121,12 @@
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
@@ -2158,14 +2173,14 @@
       <c r="H26" s="9" t="n">
         <v>37000</v>
       </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J26" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -2212,14 +2227,14 @@
       <c r="H27" s="15" t="n">
         <v>35100</v>
       </c>
-      <c r="I27" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I27" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -2268,12 +2283,12 @@
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -2322,12 +2337,12 @@
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2374,14 +2389,14 @@
       <c r="H30" s="9" t="n">
         <v>25600</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -2428,14 +2443,14 @@
       <c r="H31" s="15" t="n">
         <v>24920</v>
       </c>
-      <c r="I31" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -2484,12 +2499,12 @@
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -2536,14 +2551,14 @@
       <c r="H33" s="15" t="n">
         <v>24800</v>
       </c>
-      <c r="I33" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J33" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I33" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -2592,12 +2607,12 @@
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -2646,22 +2661,22 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Руслайн, Ямал, Скай Партнер (6 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Ямал, Скай Партнер, Аллюр Сервис (6 уник.)</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Руслайн, Ямал, Скай Партнер, Аллюр Сервис, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Ямал, Скай Партнер, Аллюр Сервис, Дримджет, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -2698,14 +2713,14 @@
       <c r="H36" s="9" t="n">
         <v>23200</v>
       </c>
-      <c r="I36" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J36" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
@@ -2754,12 +2769,12 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -2808,12 +2823,12 @@
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J38" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
@@ -2862,12 +2877,12 @@
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J39" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J39" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -2916,12 +2931,12 @@
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J40" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J40" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
@@ -2970,12 +2985,12 @@
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -3024,12 +3039,12 @@
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
@@ -3076,14 +3091,14 @@
       <c r="H43" s="15" t="n">
         <v>18600</v>
       </c>
-      <c r="I43" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J43" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -3130,14 +3145,14 @@
       <c r="H44" s="9" t="n">
         <v>17800</v>
       </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J44" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I44" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J44" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K44" s="7" t="inlineStr">
@@ -3184,14 +3199,14 @@
       <c r="H45" s="15" t="n">
         <v>17600</v>
       </c>
-      <c r="I45" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I45" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -3238,14 +3253,14 @@
       <c r="H46" s="9" t="n">
         <v>16380</v>
       </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J46" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
@@ -3294,12 +3309,12 @@
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -3348,12 +3363,12 @@
       </c>
       <c r="I48" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
@@ -3400,14 +3415,14 @@
       <c r="H49" s="15" t="n">
         <v>14000</v>
       </c>
-      <c r="I49" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -3454,14 +3469,14 @@
       <c r="H50" s="9" t="n">
         <v>13500</v>
       </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J50" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
@@ -3508,14 +3523,14 @@
       <c r="H51" s="15" t="n">
         <v>13200</v>
       </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I51" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -3564,12 +3579,12 @@
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
@@ -3618,12 +3633,12 @@
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J53" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J53" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -3672,12 +3687,12 @@
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J54" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J54" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
@@ -3726,12 +3741,12 @@
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J55" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -3780,12 +3795,12 @@
       </c>
       <c r="I56" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
@@ -3832,14 +3847,14 @@
       <c r="H57" s="15" t="n">
         <v>12000</v>
       </c>
-      <c r="I57" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J57" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -3888,12 +3903,12 @@
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J58" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J58" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K58" s="7" t="inlineStr">
@@ -3942,12 +3957,12 @@
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J59" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J59" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -3994,14 +4009,14 @@
       <c r="H60" s="9" t="n">
         <v>11400</v>
       </c>
-      <c r="I60" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J60" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I60" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
@@ -4048,14 +4063,14 @@
       <c r="H61" s="15" t="n">
         <v>10366.14</v>
       </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I61" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -4104,12 +4119,12 @@
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J62" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J62" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
@@ -4156,14 +4171,14 @@
       <c r="H63" s="15" t="n">
         <v>10000</v>
       </c>
-      <c r="I63" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I63" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -4210,14 +4225,14 @@
       <c r="H64" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="I64" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J64" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
@@ -4266,12 +4281,12 @@
       </c>
       <c r="I65" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -4318,14 +4333,14 @@
       <c r="H66" s="9" t="n">
         <v>9700</v>
       </c>
-      <c r="I66" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J66" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K66" s="7" t="inlineStr">
@@ -4374,12 +4389,12 @@
       </c>
       <c r="I67" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J67" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -4428,12 +4443,12 @@
       </c>
       <c r="I68" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J68" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K68" s="7" t="inlineStr">
@@ -4482,12 +4497,12 @@
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J69" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -4536,12 +4551,12 @@
       </c>
       <c r="I70" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
@@ -4590,12 +4605,12 @@
       </c>
       <c r="I71" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -4644,12 +4659,12 @@
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J72" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J72" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
@@ -4696,14 +4711,14 @@
       <c r="H73" s="15" t="n">
         <v>7200</v>
       </c>
-      <c r="I73" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J73" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J73" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -4752,12 +4767,12 @@
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J74" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J74" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K74" s="7" t="inlineStr">
@@ -4804,14 +4819,14 @@
       <c r="H75" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="I75" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -4858,14 +4873,14 @@
       <c r="H76" s="9" t="n">
         <v>6500</v>
       </c>
-      <c r="I76" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J76" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K76" s="7" t="inlineStr">
@@ -4914,12 +4929,12 @@
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J77" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -4968,12 +4983,12 @@
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J78" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J78" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
@@ -5022,12 +5037,12 @@
       </c>
       <c r="I79" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K79" s="13" t="inlineStr">
@@ -5076,12 +5091,12 @@
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J80" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J80" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr">
@@ -5130,12 +5145,12 @@
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J81" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J81" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K81" s="13" t="inlineStr">
@@ -5182,14 +5197,14 @@
       <c r="H82" s="9" t="n">
         <v>5400</v>
       </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I82" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr">
@@ -5238,12 +5253,12 @@
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J83" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J83" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K83" s="13" t="inlineStr">
@@ -5290,14 +5305,14 @@
       <c r="H84" s="9" t="n">
         <v>4940</v>
       </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I84" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr">
@@ -5346,12 +5361,12 @@
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J85" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J85" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K85" s="13" t="inlineStr">
@@ -5400,12 +5415,12 @@
       </c>
       <c r="I86" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J86" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J86" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K86" s="7" t="inlineStr">
@@ -5454,12 +5469,12 @@
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J87" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J87" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K87" s="13" t="inlineStr">
@@ -5508,12 +5523,12 @@
       </c>
       <c r="I88" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J88" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J88" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr">
@@ -5560,14 +5575,14 @@
       <c r="H89" s="15" t="n">
         <v>4500</v>
       </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I89" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
@@ -5614,14 +5629,14 @@
       <c r="H90" s="9" t="n">
         <v>4150</v>
       </c>
-      <c r="I90" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J90" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K90" s="7" t="inlineStr">
@@ -5668,14 +5683,14 @@
       <c r="H91" s="15" t="n">
         <v>4100</v>
       </c>
-      <c r="I91" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J91" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K91" s="13" t="inlineStr">
@@ -5722,14 +5737,14 @@
       <c r="H92" s="9" t="n">
         <v>4020</v>
       </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J92" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I92" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J92" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K92" s="7" t="inlineStr">
@@ -5778,12 +5793,12 @@
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J93" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J93" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K93" s="13" t="inlineStr">
@@ -5832,12 +5847,12 @@
       </c>
       <c r="I94" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
@@ -5886,12 +5901,12 @@
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J95" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J95" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K95" s="13" t="inlineStr">
@@ -5938,14 +5953,14 @@
       <c r="H96" s="9" t="n">
         <v>3420</v>
       </c>
-      <c r="I96" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I96" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
@@ -5992,24 +6007,24 @@
       <c r="H97" s="15" t="n">
         <v>3050</v>
       </c>
-      <c r="I97" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J97" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I97" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J97" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн (7 уник.)</t>
+          <t>Заказы ТАЗ: 6 · клиенты: Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс) (5 уник.) | Запросы ТУЗ+EXP: 13 · клиенты: Ираэро, Ямал, Nordwind, Глобал Скай (7 уник.)</t>
         </is>
       </c>
       <c r="L97" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Глобал Скай, Ираэро, Руслайн, ТАРП Авиэйшн, Ямал, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 6 (уник. №заказа+P/N; клиентов: 5 — Глобал Скай, Тулпар Эйр, Руслайн, АК Тулпар (Джет Экспресс), ЛТ Сервис, qty≈7); запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Ираэро, Ямал, Nordwind, Глобал Скай, Руслайн, qty≈26.6667). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $3,050.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $3,050.00, max $3,050.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-02-16).</t>
         </is>
       </c>
     </row>
@@ -6046,14 +6061,14 @@
       <c r="H98" s="9" t="n">
         <v>3050</v>
       </c>
-      <c r="I98" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J98" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I98" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K98" s="7" t="inlineStr">
@@ -6100,14 +6115,14 @@
       <c r="H99" s="15" t="n">
         <v>2800</v>
       </c>
-      <c r="I99" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J99" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I99" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J99" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K99" s="13" t="inlineStr">
@@ -6154,14 +6169,14 @@
       <c r="H100" s="9" t="n">
         <v>2800</v>
       </c>
-      <c r="I100" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I100" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K100" s="7" t="inlineStr">
@@ -6210,12 +6225,12 @@
       </c>
       <c r="I101" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K101" s="13" t="inlineStr">
@@ -6262,14 +6277,14 @@
       <c r="H102" s="9" t="n">
         <v>2660</v>
       </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J102" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I102" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J102" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K102" s="7" t="inlineStr">
@@ -6318,12 +6333,12 @@
       </c>
       <c r="I103" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K103" s="13" t="inlineStr">
@@ -6370,24 +6385,24 @@
       <c r="H104" s="9" t="n">
         <v>2560</v>
       </c>
-      <c r="I104" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I104" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J104" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Аэрофлот | Запросы ТУЗ+EXP: 2 · клиенты: Уральские Авиалинии, Аэрофлот (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Аэрофлот | Запросы ТУЗ+EXP: 2 · клиенты: Аэрофлот, Уральские Авиалинии (2 уник.)</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Аэрофлот, qty≈2); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Уральские Авиалинии, Аэрофлот, qty≈7). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,560.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,560.00, max $2,560.00, последний заказ 2024-09-18). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (671 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Аэрофлот, qty≈2); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Аэрофлот, Уральские Авиалинии, qty≈7). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,560.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,560.00, max $2,560.00, последний заказ 2024-09-18). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (671 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -6424,14 +6439,14 @@
       <c r="H105" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="I105" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I105" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J105" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K105" s="13" t="inlineStr">
@@ -6478,14 +6493,14 @@
       <c r="H106" s="9" t="n">
         <v>2400</v>
       </c>
-      <c r="I106" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I106" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J106" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
@@ -6534,12 +6549,12 @@
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J107" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J107" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K107" s="13" t="inlineStr">
@@ -6586,14 +6601,14 @@
       <c r="H108" s="9" t="n">
         <v>1950</v>
       </c>
-      <c r="I108" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I108" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J108" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr">
@@ -6640,14 +6655,14 @@
       <c r="H109" s="15" t="n">
         <v>1910</v>
       </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J109" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I109" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J109" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
@@ -6694,14 +6709,14 @@
       <c r="H110" s="9" t="n">
         <v>1800</v>
       </c>
-      <c r="I110" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J110" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J110" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
@@ -6748,14 +6763,14 @@
       <c r="H111" s="15" t="n">
         <v>1730</v>
       </c>
-      <c r="I111" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I111" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J111" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
@@ -6802,14 +6817,14 @@
       <c r="H112" s="9" t="n">
         <v>1656</v>
       </c>
-      <c r="I112" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I112" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J112" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
@@ -6856,14 +6871,14 @@
       <c r="H113" s="15" t="n">
         <v>1620</v>
       </c>
-      <c r="I113" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I113" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J113" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
@@ -6910,14 +6925,14 @@
       <c r="H114" s="9" t="n">
         <v>1248</v>
       </c>
-      <c r="I114" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J114" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J114" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K114" s="7" t="inlineStr">
@@ -6966,12 +6981,12 @@
       </c>
       <c r="I115" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J115" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J115" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K115" s="13" t="inlineStr">
@@ -7020,12 +7035,12 @@
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J116" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J116" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr">
@@ -7072,14 +7087,14 @@
       <c r="H117" s="15" t="n">
         <v>1000</v>
       </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J117" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I117" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J117" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
@@ -7128,12 +7143,12 @@
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J118" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J118" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K118" s="7" t="inlineStr">
@@ -7182,12 +7197,12 @@
       </c>
       <c r="I119" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K119" s="13" t="inlineStr">
@@ -7236,12 +7251,12 @@
       </c>
       <c r="I120" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
@@ -7290,12 +7305,12 @@
       </c>
       <c r="I121" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K121" s="13" t="inlineStr">
@@ -7344,12 +7359,12 @@
       </c>
       <c r="I122" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K122" s="7" t="inlineStr">
@@ -7398,12 +7413,12 @@
       </c>
       <c r="I123" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K123" s="13" t="inlineStr">
@@ -7450,14 +7465,14 @@
       <c r="H124" s="9" t="n">
         <v>686</v>
       </c>
-      <c r="I124" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J124" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J124" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K124" s="7" t="inlineStr">
@@ -7504,14 +7519,14 @@
       <c r="H125" s="15" t="n">
         <v>670</v>
       </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J125" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I125" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J125" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K125" s="13" t="inlineStr">
@@ -7558,14 +7573,14 @@
       <c r="H126" s="9" t="n">
         <v>635</v>
       </c>
-      <c r="I126" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J126" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J126" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
@@ -7612,24 +7627,24 @@
       <c r="H127" s="15" t="n">
         <v>630.5</v>
       </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J127" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I127" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J127" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Utair, Победа, Аэрофлот, Уральские Авиалинии (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Аэрофлот, Уральские Авиалинии, Utair, Победа (4 уник.)</t>
         </is>
       </c>
       <c r="L127" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Utair, Победа, Аэрофлот, Уральские Авиалинии, qty≈69). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $48.50: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $48.00, max $49.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Аэрофлот, Уральские Авиалинии, Utair, Победа, qty≈69). Сопоставление: ALT P/N, точное P/N. На складе: 13 шт. (2 строк АТИ). Состояние склада: NEW. Ориентир $48.50: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $48.00, max $49.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7683,12 @@
       </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J128" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J128" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K128" s="7" t="inlineStr">
@@ -7722,12 +7737,12 @@
       </c>
       <c r="I129" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J129" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K129" s="13" t="inlineStr">
@@ -7774,14 +7789,14 @@
       <c r="H130" s="9" t="n">
         <v>550</v>
       </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J130" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I130" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K130" s="7" t="inlineStr">
@@ -7830,22 +7845,22 @@
       </c>
       <c r="I131" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J131" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Русджет, Дримджет, ЮВТ (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Уральские Авиалинии, ЮВТ, Тулпар Техник, Аллюр Сервис (13 уник.)</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — Руслайн, Русджет, Дримджет, ЮВТ, Тулпар Техник, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет, Тулпар Техник, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Уральские Авиалинии, ЮВТ, Тулпар Техник, Аллюр Сервис, Северо-Запад, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -7884,22 +7899,22 @@
       </c>
       <c r="I132" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J132" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Ямал, СмартАвиа, Алроса, Ай Флай (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Ямал | Запросы ТУЗ+EXP: 4 · клиенты: Ай Флай, Алроса, Ямал, СмартАвиа (4 уник.)</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Ямал, СмартАвиа, Алроса, Ай Флай, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Ямал, qty≈50); запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 4 — Ай Флай, Алроса, Ямал, СмартАвиа, qty≈63). Сопоставление: ALT P/N, точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $101.00: медиана продажных цен ТАЗ (все даты) (n=1, min $101.00, max $101.00, последний заказ 2024-07-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (721 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -7936,14 +7951,14 @@
       <c r="H133" s="15" t="n">
         <v>500</v>
       </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J133" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I133" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J133" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
@@ -7990,14 +8005,14 @@
       <c r="H134" s="9" t="n">
         <v>470</v>
       </c>
-      <c r="I134" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I134" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J134" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K134" s="7" t="inlineStr">
@@ -8044,24 +8059,24 @@
       <c r="H135" s="15" t="n">
         <v>426</v>
       </c>
-      <c r="I135" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J135" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I135" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J135" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K135" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Nordwind, Аэрофлот Техникс (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Аэрофлот Техникс, Nordwind (3 уник.)</t>
         </is>
       </c>
       <c r="L135" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Nordwind, Аэрофлот Техникс, qty≈115.25). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Аэрофлот Техникс, Nordwind, qty≈142). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $213.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=6, min $127.00, max $310.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -8100,12 +8115,12 @@
       </c>
       <c r="I136" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J136" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J136" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K136" s="7" t="inlineStr">
@@ -8152,24 +8167,24 @@
       <c r="H137" s="15" t="n">
         <v>406</v>
       </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J137" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I137" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J137" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K137" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Аэрофлот, Северо-Запад, Аэрофлот Техникс (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Северо-Запад, Аэрофлот Техникс, Аэрофлот (3 уник.)</t>
         </is>
       </c>
       <c r="L137" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Аэрофлот, Северо-Запад, Аэрофлот Техникс, qty≈66). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $203.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $190.00, max $216.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 3 — Северо-Запад, Аэрофлот Техникс, Аэрофлот, qty≈66). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 2 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $203.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $190.00, max $216.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -8206,14 +8221,14 @@
       <c r="H138" s="9" t="n">
         <v>402</v>
       </c>
-      <c r="I138" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J138" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J138" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K138" s="7" t="inlineStr">
@@ -8260,14 +8275,14 @@
       <c r="H139" s="15" t="n">
         <v>384</v>
       </c>
-      <c r="I139" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J139" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I139" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J139" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K139" s="13" t="inlineStr">
@@ -8314,14 +8329,14 @@
       <c r="H140" s="9" t="n">
         <v>380</v>
       </c>
-      <c r="I140" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I140" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J140" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K140" s="7" t="inlineStr">
@@ -8370,12 +8385,12 @@
       </c>
       <c r="I141" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J141" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K141" s="13" t="inlineStr">
@@ -8424,12 +8439,12 @@
       </c>
       <c r="I142" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J142" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J142" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K142" s="7" t="inlineStr">
@@ -8476,14 +8491,14 @@
       <c r="H143" s="15" t="n">
         <v>346</v>
       </c>
-      <c r="I143" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J143" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I143" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J143" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K143" s="13" t="inlineStr">
@@ -8530,14 +8545,14 @@
       <c r="H144" s="9" t="n">
         <v>340</v>
       </c>
-      <c r="I144" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J144" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J144" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K144" s="7" t="inlineStr">
@@ -8584,14 +8599,14 @@
       <c r="H145" s="15" t="n">
         <v>330</v>
       </c>
-      <c r="I145" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J145" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I145" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J145" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K145" s="13" t="inlineStr">
@@ -8640,12 +8655,12 @@
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J146" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J146" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K146" s="7" t="inlineStr">
@@ -8692,14 +8707,14 @@
       <c r="H147" s="15" t="n">
         <v>308</v>
       </c>
-      <c r="I147" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J147" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I147" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J147" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K147" s="13" t="inlineStr">
@@ -8748,12 +8763,12 @@
       </c>
       <c r="I148" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J148" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K148" s="7" t="inlineStr">
@@ -8800,14 +8815,14 @@
       <c r="H149" s="15" t="n">
         <v>284</v>
       </c>
-      <c r="I149" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J149" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I149" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J149" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K149" s="13" t="inlineStr">
@@ -8856,22 +8871,22 @@
       </c>
       <c r="I150" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J150" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
         </is>
       </c>
       <c r="L150" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -8908,14 +8923,14 @@
       <c r="H151" s="15" t="n">
         <v>256</v>
       </c>
-      <c r="I151" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J151" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I151" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J151" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K151" s="13" t="inlineStr">
@@ -8964,12 +8979,12 @@
       </c>
       <c r="I152" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J152" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K152" s="7" t="inlineStr">
@@ -9016,14 +9031,14 @@
       <c r="H153" s="15" t="n">
         <v>180</v>
       </c>
-      <c r="I153" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I153" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J153" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K153" s="13" t="inlineStr">
@@ -9072,12 +9087,12 @@
       </c>
       <c r="I154" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J154" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J154" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K154" s="7" t="inlineStr">
@@ -9126,12 +9141,12 @@
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J155" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J155" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K155" s="13" t="inlineStr">
@@ -9180,12 +9195,12 @@
       </c>
       <c r="I156" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J156" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K156" s="7" t="inlineStr">
@@ -9234,12 +9249,12 @@
       </c>
       <c r="I157" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J157" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K157" s="13" t="inlineStr">
@@ -9288,12 +9303,12 @@
       </c>
       <c r="I158" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J158" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K158" s="7" t="inlineStr">
@@ -9340,14 +9355,14 @@
       <c r="H159" s="15" t="n">
         <v>111</v>
       </c>
-      <c r="I159" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J159" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I159" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J159" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K159" s="13" t="inlineStr">
@@ -9394,14 +9409,14 @@
       <c r="H160" s="9" t="n">
         <v>76</v>
       </c>
-      <c r="I160" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J160" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I160" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J160" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K160" s="7" t="inlineStr">
@@ -9448,14 +9463,14 @@
       <c r="H161" s="15" t="n">
         <v>62</v>
       </c>
-      <c r="I161" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I161" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J161" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K161" s="13" t="inlineStr">
@@ -9502,14 +9517,14 @@
       <c r="H162" s="9" t="n">
         <v>56</v>
       </c>
-      <c r="I162" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I162" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J162" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K162" s="7" t="inlineStr">
@@ -9556,14 +9571,14 @@
       <c r="H163" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J163" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I163" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J163" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K163" s="13" t="inlineStr">
@@ -9610,14 +9625,14 @@
       <c r="H164" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="I164" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I164" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J164" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K164" s="7" t="inlineStr">
@@ -9666,12 +9681,12 @@
       </c>
       <c r="I165" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J165" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K165" s="13" t="inlineStr">
@@ -9718,14 +9733,14 @@
       <c r="H166" s="9" t="n">
         <v>3.4</v>
       </c>
-      <c r="I166" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J166" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I166" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J166" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K166" s="7" t="inlineStr">
@@ -9772,14 +9787,14 @@
       <c r="H167" s="15" t="n">
         <v>3.2</v>
       </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J167" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I167" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J167" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K167" s="13" t="inlineStr">
@@ -9828,12 +9843,12 @@
       </c>
       <c r="I168" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J168" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K168" s="7" t="inlineStr">
@@ -9878,12 +9893,12 @@
       <c r="H169" s="12" t="n"/>
       <c r="I169" s="17" t="inlineStr">
         <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J169" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J169" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K169" s="13" t="inlineStr">
@@ -9926,14 +9941,14 @@
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="6" t="n"/>
-      <c r="I170" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J170" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J170" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K170" s="7" t="inlineStr">
@@ -9976,14 +9991,14 @@
       </c>
       <c r="G171" s="12" t="n"/>
       <c r="H171" s="12" t="n"/>
-      <c r="I171" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J171" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J171" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K171" s="13" t="inlineStr">
@@ -10026,14 +10041,14 @@
       </c>
       <c r="G172" s="6" t="n"/>
       <c r="H172" s="6" t="n"/>
-      <c r="I172" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J172" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J172" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K172" s="7" t="inlineStr">
@@ -10076,14 +10091,14 @@
       </c>
       <c r="G173" s="12" t="n"/>
       <c r="H173" s="12" t="n"/>
-      <c r="I173" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J173" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J173" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K173" s="13" t="inlineStr">
@@ -10126,14 +10141,14 @@
       </c>
       <c r="G174" s="6" t="n"/>
       <c r="H174" s="6" t="n"/>
-      <c r="I174" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J174" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J174" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K174" s="7" t="inlineStr">
@@ -10176,14 +10191,14 @@
       </c>
       <c r="G175" s="12" t="n"/>
       <c r="H175" s="12" t="n"/>
-      <c r="I175" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J175" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J175" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K175" s="13" t="inlineStr">
@@ -10226,14 +10241,14 @@
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="6" t="n"/>
-      <c r="I176" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J176" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J176" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K176" s="7" t="inlineStr">
@@ -10277,62 +10292,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>Ранг</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>Тип ВС</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="21" t="inlineStr">
         <is>
           <t>P/N</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="21" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="21" t="inlineStr">
         <is>
           <t>Состояние</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="21" t="inlineStr">
         <is>
           <t>Кол-во на складе Utair</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="21" t="inlineStr">
         <is>
           <t>Ориентировочная цена USD</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="H1" s="21" t="inlineStr">
         <is>
           <t>Потенц. выручка USD</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
-        <is>
-          <t>Уверенность</t>
-        </is>
-      </c>
-      <c r="J1" s="18" t="inlineStr">
-        <is>
-          <t>Флаг цены</t>
-        </is>
-      </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="I1" s="21" t="inlineStr">
+        <is>
+          <t>Ликвидность</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Уверенность в цене</t>
+        </is>
+      </c>
+      <c r="K1" s="21" t="inlineStr">
         <is>
           <t>Спрос (заказы/запросы)</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="L1" s="21" t="inlineStr">
         <is>
           <t>Обоснование оценки</t>
         </is>
@@ -10371,14 +10386,14 @@
       <c r="H2" s="9" t="n">
         <v>363200</v>
       </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J2" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J2" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -10425,14 +10440,14 @@
       <c r="H3" s="15" t="n">
         <v>184500</v>
       </c>
-      <c r="I3" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
@@ -10481,12 +10496,12 @@
       </c>
       <c r="I4" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -10535,12 +10550,12 @@
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -10587,14 +10602,14 @@
       <c r="H6" s="9" t="n">
         <v>34500</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -10641,14 +10656,14 @@
       <c r="H7" s="15" t="n">
         <v>32800</v>
       </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -10697,12 +10712,12 @@
       </c>
       <c r="I8" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -10751,12 +10766,12 @@
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -10803,14 +10818,14 @@
       <c r="H10" s="9" t="n">
         <v>19600</v>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -10857,24 +10872,24 @@
       <c r="H11" s="15" t="n">
         <v>18900</v>
       </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J11" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: ЮВТ, ТАУ Центр, Тулпар Техник, Ямал (5 уник.)</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, Руслайн, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
         </is>
       </c>
     </row>
@@ -10913,12 +10928,12 @@
       </c>
       <c r="I12" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -10965,24 +10980,24 @@
       <c r="H13" s="15" t="n">
         <v>16100</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Руслайн, Ираэро (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Руслайн (2 уник.)</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Ираэро, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
         </is>
       </c>
     </row>
@@ -11021,12 +11036,12 @@
       </c>
       <c r="I14" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -11073,14 +11088,14 @@
       <c r="H15" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J15" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
@@ -11129,12 +11144,12 @@
       </c>
       <c r="I16" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -11183,12 +11198,12 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J17" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J17" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -11237,12 +11252,12 @@
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -11289,14 +11304,14 @@
       <c r="H19" s="15" t="n">
         <v>9700</v>
       </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I19" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J19" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
@@ -11343,14 +11358,14 @@
       <c r="H20" s="9" t="n">
         <v>8450</v>
       </c>
-      <c r="I20" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -11399,12 +11414,12 @@
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -11453,12 +11468,12 @@
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -11507,12 +11522,12 @@
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
@@ -11561,12 +11576,12 @@
       </c>
       <c r="I24" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J24" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -11615,12 +11630,12 @@
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
@@ -11667,14 +11682,14 @@
       <c r="H26" s="9" t="n">
         <v>7000</v>
       </c>
-      <c r="I26" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J26" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -11723,12 +11738,12 @@
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -11775,14 +11790,14 @@
       <c r="H28" s="9" t="n">
         <v>5400</v>
       </c>
-      <c r="I28" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -11829,14 +11844,14 @@
       <c r="H29" s="15" t="n">
         <v>5000</v>
       </c>
-      <c r="I29" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -11883,14 +11898,14 @@
       <c r="H30" s="9" t="n">
         <v>4600</v>
       </c>
-      <c r="I30" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I30" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -11937,14 +11952,14 @@
       <c r="H31" s="15" t="n">
         <v>4150</v>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
-        </is>
-      </c>
-      <c r="J31" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -11993,12 +12008,12 @@
       </c>
       <c r="I32" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -12042,62 +12057,62 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Ранг</t>
         </is>
       </c>
-      <c r="B1" s="19" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Тип ВС</t>
         </is>
       </c>
-      <c r="C1" s="19" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>P/N</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="22" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="E1" s="19" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>Состояние</t>
         </is>
       </c>
-      <c r="F1" s="19" t="inlineStr">
+      <c r="F1" s="22" t="inlineStr">
         <is>
           <t>Кол-во на складе Utair</t>
         </is>
       </c>
-      <c r="G1" s="19" t="inlineStr">
+      <c r="G1" s="22" t="inlineStr">
         <is>
           <t>Ориентировочная цена USD</t>
         </is>
       </c>
-      <c r="H1" s="19" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>Потенц. выручка USD</t>
         </is>
       </c>
-      <c r="I1" s="19" t="inlineStr">
-        <is>
-          <t>Уверенность</t>
-        </is>
-      </c>
-      <c r="J1" s="19" t="inlineStr">
-        <is>
-          <t>Флаг цены</t>
-        </is>
-      </c>
-      <c r="K1" s="19" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
+        <is>
+          <t>Ликвидность</t>
+        </is>
+      </c>
+      <c r="J1" s="22" t="inlineStr">
+        <is>
+          <t>Уверенность в цене</t>
+        </is>
+      </c>
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>Спрос (заказы/запросы)</t>
         </is>
       </c>
-      <c r="L1" s="19" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>Обоснование оценки</t>
         </is>
@@ -12138,12 +12153,12 @@
       </c>
       <c r="I2" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J2" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -12190,14 +12205,14 @@
       <c r="H3" s="15" t="n">
         <v>28524</v>
       </c>
-      <c r="I3" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J3" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J3" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K3" s="13" t="inlineStr">
@@ -12246,12 +12261,12 @@
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J4" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J4" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -12298,14 +12313,14 @@
       <c r="H5" s="15" t="n">
         <v>7450</v>
       </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J5" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
@@ -12354,12 +12369,12 @@
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J6" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -12408,12 +12423,12 @@
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J7" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -12460,14 +12475,14 @@
       <c r="H8" s="9" t="n">
         <v>5190</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
@@ -12516,12 +12531,12 @@
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J9" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J9" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -12568,14 +12583,14 @@
       <c r="H10" s="9" t="n">
         <v>4320</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J10" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K10" s="7" t="inlineStr">
@@ -12624,12 +12639,12 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
@@ -12676,14 +12691,14 @@
       <c r="H12" s="9" t="n">
         <v>2840</v>
       </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
@@ -12730,14 +12745,14 @@
       <c r="H13" s="15" t="n">
         <v>2632</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J13" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
@@ -12784,14 +12799,14 @@
       <c r="H14" s="9" t="n">
         <v>2500</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J14" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
@@ -12838,14 +12853,14 @@
       <c r="H15" s="15" t="n">
         <v>1910</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J15" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I15" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
@@ -12892,14 +12907,14 @@
       <c r="H16" s="9" t="n">
         <v>1900</v>
       </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
@@ -12948,12 +12963,12 @@
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -13000,14 +13015,14 @@
       <c r="H18" s="9" t="n">
         <v>1600</v>
       </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J18" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J18" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
@@ -13054,14 +13069,14 @@
       <c r="H19" s="15" t="n">
         <v>1370</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J19" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
@@ -13108,14 +13123,14 @@
       <c r="H20" s="9" t="n">
         <v>1170</v>
       </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
@@ -13164,12 +13179,12 @@
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J21" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -13216,14 +13231,14 @@
       <c r="H22" s="9" t="n">
         <v>1038</v>
       </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J22" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
@@ -13272,12 +13287,12 @@
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
@@ -13324,14 +13339,14 @@
       <c r="H24" s="9" t="n">
         <v>720</v>
       </c>
-      <c r="I24" s="11" t="inlineStr">
-        <is>
-          <t>высокая</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>есть заказы</t>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J24" s="19" t="inlineStr">
+        <is>
+          <t>высокая (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
@@ -13378,14 +13393,14 @@
       <c r="H25" s="15" t="n">
         <v>670</v>
       </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J25" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I25" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
@@ -13434,12 +13449,12 @@
       </c>
       <c r="I26" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K26" s="7" t="inlineStr">
@@ -13488,12 +13503,12 @@
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J27" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -13540,14 +13555,14 @@
       <c r="H28" s="9" t="n">
         <v>530</v>
       </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J28" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I28" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J28" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K28" s="7" t="inlineStr">
@@ -13594,14 +13609,14 @@
       <c r="H29" s="15" t="n">
         <v>440</v>
       </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J29" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I29" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J29" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -13650,12 +13665,12 @@
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J30" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J30" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
@@ -13702,14 +13717,14 @@
       <c r="H31" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="I31" s="10" t="inlineStr">
-        <is>
-          <t>средняя</t>
+      <c r="I31" s="17" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -13756,14 +13771,14 @@
       <c r="H32" s="9" t="n">
         <v>284</v>
       </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J32" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J32" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
@@ -13812,12 +13827,12 @@
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -13866,12 +13881,12 @@
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
-          <t>низкая</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>есть предложения</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J34" s="18" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -13920,12 +13935,12 @@
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J35" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -13974,12 +13989,12 @@
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
@@ -14028,12 +14043,12 @@
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -14082,12 +14097,12 @@
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
@@ -14136,22 +14151,22 @@
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
-          <t>средняя</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>есть заказы</t>
+          <t>средняя (заказы ТАЗ)</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Уральские Авиалинии | Запросы ТУЗ+EXP: 5 · клиенты: S7 Engineering, UTG, Ямал, 407 Техникс (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Уральские Авиалинии | Запросы ТУЗ+EXP: 5 · клиенты: UTG, Ямал, 407 Техникс, S7 Engineering (4 уник.)</t>
         </is>
       </c>
       <c r="L39" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Уральские Авиалинии, qty≈500); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — S7 Engineering, UTG, Ямал, 407 Техникс, qty≈2042.4). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $2.80: медиана продажных цен ТАЗ (все даты) (n=1, min $2.80, max $2.80, последний заказ 2024-05-31). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (781 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Уральские Авиалинии, qty≈500); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — UTG, Ямал, 407 Техникс, S7 Engineering, qty≈1303). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $2.80: медиана продажных цен ТАЗ (все даты) (n=1, min $2.80, max $2.80, последний заказ 2024-05-31). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (781 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -14184,14 +14199,14 @@
       </c>
       <c r="G40" s="6" t="n"/>
       <c r="H40" s="6" t="n"/>
-      <c r="I40" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J40" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
@@ -14234,14 +14249,14 @@
       </c>
       <c r="G41" s="12" t="n"/>
       <c r="H41" s="12" t="n"/>
-      <c r="I41" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J41" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -14284,14 +14299,14 @@
       </c>
       <c r="G42" s="6" t="n"/>
       <c r="H42" s="6" t="n"/>
-      <c r="I42" s="17" t="inlineStr">
-        <is>
-          <t>н/п</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>есть запросы, но нет предложений</t>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J42" s="20" t="inlineStr">
+        <is>
+          <t>н/п (запросы без предложений)</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
@@ -14332,7 +14347,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -14344,7 +14359,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -14356,7 +14371,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>C</t>
         </is>

--- a/output/ATI_buyout_recommendations_internal.xlsx
+++ b/output/ATI_buyout_recommendations_internal.xlsx
@@ -18,8 +18,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1. Сервис ликвидный'!$A$1:$L$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2. Сервис неликвидный'!$A$1:$L$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Ансервис ликвидный'!$A$1:$L$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. Ансервис неликвидный'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3. Ансервис ликвидный'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'4. Ансервис неликвидный'!$A$1:$L$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'5. Неизвестное'!$A$1:$L$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -613,7 +613,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Дата: 2026-07-30 13:01 | Ликвидные = A/B; неликвидные = C (сильный C: спрос ≥2 или выручка ≥ $3 000)</t>
+          <t>Дата: 2026-07-30 13:22 | Ликвидные = A/B; неликвидные = C (сильный C: спрос ≥2 или выручка ≥ $3 000)</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3984765.61</v>
+        <v>3875965.61</v>
       </c>
     </row>
     <row r="17">
@@ -1243,12 +1243,12 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: ЮВТ, ТАУ Центр, Тулпар Техник, Ямал (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник (5 уник.)</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, Руслайн, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Ямал, Скай Партнер, Аллюр Сервис (6 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 17 · клиенты: ЮВТ, Руслайн, Ямал, Скай Партнер (6 уник.)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Ямал, Скай Партнер, Аллюр Сервис, Дримджет, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 17 (уник. P/N+клиент+день; клиентов: 6 — ЮВТ, Руслайн, Ямал, Скай Партнер, Аллюр Сервис, qty≈18). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $12,300.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=11, min $3,900.00, max $24,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 7 · клиенты: Белавиа, Аэрофлот, S7 Engineering, АК Сибирь (5 уник.)</t>
+          <t>Заказы ТАЗ: 2 · клиенты: Белавиа | Запросы ТУЗ+EXP: 8 · клиенты: Белавиа, S7, АК Сибирь, S7 Engineering (6 уник.)</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 7 (уник. P/N+клиент+день; клиентов: 5 — Белавиа, Аэрофлот, S7 Engineering, АК Сибирь, Уральские Авиалинии, qty≈11.25). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 2 (уник. №заказа+P/N; клиентов: 1 — Белавиа, qty≈2); запросов ТУЗ+EXP: 8 (уник. P/N+клиент+день; клиентов: 6 — Белавиа, S7, АК Сибирь, S7 Engineering, Уральские Авиалинии, qty≈12.5). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $4,100.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $3,200.00, max $5,000.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-05-07).</t>
         </is>
       </c>
     </row>
@@ -3241,12 +3241,12 @@
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Русджет, Дримджет, ЮВТ (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет (13 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Руслайн, Русджет (5 уник.) | Запросы ТУЗ+EXP: 25 · клиенты: Уральские Авиалинии, ЮВТ, Тулпар Техник, АК Тулпар (13 уник.)</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — Руслайн, Русджет, Дримджет, ЮВТ, Тулпар Техник, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — АК Тулпар, Северо-Запад, Аллюр Сервис, Русджет, Тулпар Техник, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Руслайн, Русджет, Дримджет, qty≈237); запросов ТУЗ+EXP: 25 (уник. P/N+клиент+день; клиентов: 13 — Уральские Авиалинии, ЮВТ, Тулпар Техник, АК Тулпар, Северо-Запад, qty≈164). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 56 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $9.70: медиана продажных цен ТАЗ (все даты) (n=6, min $4.50, max $41.00, последний заказ 2025-10-30). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (264 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3349,12 @@
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Nordwind, Уральские Авиалинии, -, Аэрофлот (7 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 13 · клиенты: Аэрофлот, АК Россия, S7 Engineering, СмартАвиа (7 уник.)</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Nordwind, Уральские Авиалинии, -, Аэрофлот, АК Россия, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 13 (уник. P/N+клиент+день; клиентов: 7 — Аэрофлот, АК Россия, S7 Engineering, СмартАвиа, Nordwind, qty≈94). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=7, min $260.00, max $5,700.00, последнее предложение 2025-01-30). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 537 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 9 · клиенты: Nordwind, Уральские Авиалинии, Аэрофлот, Аэрофлот Техникс (5 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 9 · клиенты: Ямал, Nordwind, Аэрофлот, Уральские Авиалинии (5 уник.)</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 9 (уник. P/N+клиент+день; клиентов: 5 — Nordwind, Уральские Авиалинии, Аэрофлот, Аэрофлот Техникс, Ямал, qty≈151.6). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $134.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $130.00, max $160.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
+          <t>Ликвидность A (высокая). запросов ТУЗ+EXP: 9 (уник. P/N+клиент+день; клиентов: 5 — Ямал, Nordwind, Аэрофлот, Уральские Авиалинии, Аэрофлот Техникс, qty≈143.714). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 3 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $134.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $130.00, max $160.00). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние или без даты.</t>
         </is>
       </c>
     </row>
@@ -3565,12 +3565,12 @@
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: Руслайн, ЮВТ, Ямал (3 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: Руслайн, Дримджет (2 уник.) | Запросы ТУЗ+EXP: 5 · клиенты: ЮВТ, Руслайн, Ямал (3 уник.)</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 2 — Руслайн, Дримджет, qty≈27); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Руслайн, ЮВТ, Ямал, qty≈27). Сопоставление: ALT P/N, ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $340.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $300.00, max $380.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-07).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 2 — Руслайн, Дримджет, qty≈27); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — ЮВТ, Руслайн, Ямал, qty≈26.3333). Сопоставление: ALT P/N, ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $340.00: медиана продажных цен ТАЗ за последние 6 мес. (n=2, min $300.00, max $380.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-07).</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Авиасервис, Дримджет, АК Тулпар (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: АК Тулпар (Джет Экспресс) | Запросы ТУЗ+EXP: 6 · клиенты: АК Тулпар, Авиасервис, ЮВТ, Дримджет (4 уник.)</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — ЮВТ, Авиасервис, Дримджет, АК Тулпар, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — АК Тулпар (Джет Экспресс), qty≈10); запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 4 — АК Тулпар, Авиасервис, ЮВТ, Дримджет, qty≈123). Сопоставление: ALT P/N, точное P/N. На складе: 12 шт. (1 строк АТИ). Состояние склада: SERVICEABLE?. Ориентир $22.00: медиана продажных цен ТАЗ (все даты) (n=1, min $22.00, max $22.00, последний заказ 2023-09-26). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1029 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -4807,12 +4807,12 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: АК Тулпар (Джет Экспресс), АК Тулпар, Аллюр Сервис (3 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: АК Тулпар, Аллюр Сервис, АК Тулпар (Джет Экспресс) (3 уник.)</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар (Джет Экспресс), АК Тулпар, Аллюр Сервис, qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $5,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,700.00, max $5,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — АК Тулпар, Аллюр Сервис, АК Тулпар (Джет Экспресс), qty≈5). Сопоставление: ALT P/N, точное P/N. На складе: 2 шт. (2 строк АТИ). Состояние склада: OVERHAULED; REPAIRED / BER?. Ориентир $5,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,700.00, max $5,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="K87" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Аэрофлот | Запросы ТУЗ+EXP: 2 · клиенты: Уральские Авиалинии, Аэрофлот (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Аэрофлот | Запросы ТУЗ+EXP: 2 · клиенты: Аэрофлот, Уральские Авиалинии (2 уник.)</t>
         </is>
       </c>
       <c r="L87" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Аэрофлот, qty≈2); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Уральские Авиалинии, Аэрофлот, qty≈7). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,560.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,560.00, max $2,560.00, последний заказ 2024-09-18). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (671 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Аэрофлот, qty≈2); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Аэрофлот, Уральские Авиалинии, qty≈7). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,560.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,560.00, max $2,560.00, последний заказ 2024-09-18). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (671 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Азур Эйр | Запросы ТУЗ+EXP: 5 · клиенты: Азур Эйр, Аэрофлот (2 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Азур Эйр | Запросы ТУЗ+EXP: 5 · клиенты: Аэрофлот, Азур Эйр (2 уник.)</t>
         </is>
       </c>
       <c r="L89" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Азур Эйр, qty≈2); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 2 — Азур Эйр, Аэрофлот, qty≈7). Сопоставление: ведущие нули, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,400.00, max $2,400.00, последний заказ 2024-01-12). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (921 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Азур Эйр, qty≈2); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 2 — Аэрофлот, Азур Эйр, qty≈7). Сопоставление: ведущие нули, нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: NEW. Ориентир $2,400.00: медиана продажных цен ТАЗ (все даты) (n=1, min $2,400.00, max $2,400.00, последний заказ 2024-01-12). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (921 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -7594,12 +7594,12 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Ираэро, Руслайн (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Руслайн, Ираэро (2 уник.)</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈2). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 10 шт. (5 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $3,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $3,700.00, max $3,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-05-05.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Ираэро, qty≈2). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 10 шт. (5 строк АТИ). Состояние склада: SERVICEABLE. Ориентир $3,700.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $3,700.00, max $3,700.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-05-05.</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: Северсталь, ЮВТ (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 3 · клиенты: ЮВТ, Северсталь (2 уник.)</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 2 — Северсталь, ЮВТ, qty≈17). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW; SERVICEABLE. Ориентировочная цена не рассчитана: нет «Продажная, ед.» в ТАЗ и нет Offered/Sell Price в ТУЗ/EXP. ВНИМАНИЕ: спрос/заказы есть, но sell/offered цены нет — денежная оценка невозможна.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 3 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Северсталь, qty≈17). Сопоставление: ALT P/N, точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: NEW; SERVICEABLE. Ориентировочная цена не рассчитана: нет «Продажная, ед.» в ТАЗ и нет Offered/Sell Price в ТУЗ/EXP. ВНИМАНИЕ: спрос/заказы есть, но sell/offered цены нет — денежная оценка невозможна.</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10789,12 +10789,12 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: ЮВТ, ТАУ Центр, Тулпар Техник, Ямал (5 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Руслайн | Запросы ТУЗ+EXP: 10 · клиенты: Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник (5 уник.)</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, Руслайн, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Руслайн, qty≈1); запросов ТУЗ+EXP: 10 (уник. P/N+клиент+день; клиентов: 5 — Руслайн, ЮВТ, ТАУ Центр, Тулпар Техник, Ямал, qty≈11). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $18,900.00: медиана продажных цен ТАЗ за последние 6 мес. (n=1, min $18,900.00, max $18,900.00). уверенность высокая: есть заказ(и) ТАЗ с продажной ценой за последние 180 дн. (последний 2026-07-14).</t>
         </is>
       </c>
     </row>
@@ -11005,12 +11005,12 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро (7 уник.)</t>
+          <t>Заказы ТАЗ: 4 · клиенты: Ираэро, Руслайн, Дримджет (3 уник.) | Запросы ТУЗ+EXP: 12 · клиенты: ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр (7 уник.)</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — Тулпар Эйр, Ираэро, Руслайн, Тулпар Аэро, Аллюр Сервис, qty≈12.8). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 4 (уник. №заказа+P/N; клиентов: 3 — Ираэро, Руслайн, Дримджет, qty≈4); запросов ТУЗ+EXP: 12 (уник. P/N+клиент+день; клиентов: 7 — ЮВТ, Руслайн, АК Тулпар, Тулпар Эйр, Ираэро, qty≈13). Сопоставление: ALT P/N, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $13,700.00: медиана продажных цен ТАЗ (все даты) (n=3, min $13,150.00, max $14,000.00, последний заказ 2025-09-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (300 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -11344,17 +11344,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>B738</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>930-6201-001</t>
+          <t>2612311-1</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>CONTROL UNIT-WEATHER RADAR</t>
+          <t>WHEEL ASSY - MLG</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -11363,32 +11363,32 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>34500</v>
+        <v>7950</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>34500</v>
+        <v>254400</v>
       </c>
       <c r="I18" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>низкая (предложения)</t>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Nordwind, S7 Engineering, Аэрофлот, АК Сибирь (4 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Белавиа, S7, Аэрофлот (3 уник.)</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Nordwind, S7 Engineering, Аэрофлот, АК Сибирь, qty≈5). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $34,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $22,500.00, max $57,100.00, последнее предложение 2025-07-08). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 378 дн. назад).</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 3 — Белавиа, S7, Аэрофлот, qty≈8). Сопоставление: точное P/N. На складе: 32 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $7,950.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=4, min $4,000.00, max $13,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-07.</t>
         </is>
       </c>
     </row>
@@ -11398,17 +11398,17 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>S800-3000-00</t>
+          <t>930-6201-001</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>RECORDER, FLIGHT DATA</t>
+          <t>CONTROL UNIT-WEATHER RADAR</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
@@ -11420,29 +11420,29 @@
         <v>1</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>16100</v>
+        <v>34500</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>16100</v>
+        <v>34500</v>
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>средняя (предложения)</t>
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Руслайн (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 5 · клиенты: Nordwind, S7 Engineering, Аэрофлот, АК Сибирь (4 уник.)</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — Nordwind, S7 Engineering, Аэрофлот, АК Сибирь, qty≈5). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $34,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=3, min $22,500.00, max $57,100.00, последнее предложение 2025-07-08). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 378 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -11457,12 +11457,12 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>27600-3</t>
+          <t>S800-3000-00</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>VALVE ASSY</t>
+          <t>RECORDER, FLIGHT DATA</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -11474,10 +11474,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>9700</v>
+        <v>16100</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>9700</v>
+        <v>16100</v>
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
@@ -11486,17 +11486,17 @@
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>средняя (заказы ТАЗ)</t>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 2 · клиенты: Тулпар Эйр, Дримджет (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: Ираэро, Руслайн (2 уник.)</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈4); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Тулпар Эйр, Дримджет, qty≈5). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $9,700.00: медиана продажных цен ТАЗ (все даты) (n=1, min $9,700.00, max $9,700.00, последний заказ 2025-06-16). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (400 дн. назад).</t>
+          <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — Ираэро, Руслайн, qty≈6). Сопоставление: нормализация (дефисы/пробелы), точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $16,100.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $10,500.00, max $19,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-09.</t>
         </is>
       </c>
     </row>
@@ -11511,12 +11511,12 @@
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>2LA006178-02</t>
+          <t>27600-3</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>FLOODLIGHT UNIT-FIRST OFFICER</t>
+          <t>VALVE ASSY</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -11528,10 +11528,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>8450</v>
+        <v>9700</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>8450</v>
+        <v>9700</v>
       </c>
       <c r="I21" s="18" t="inlineStr">
         <is>
@@ -11545,12 +11545,12 @@
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Джет Экспресс | Запросы ТУЗ+EXP: 1 · клиенты: -</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Тулпар Эйр | Запросы ТУЗ+EXP: 2 · клиенты: Тулпар Эйр, Дримджет (2 уник.)</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Джет Экспресс, qty≈1); запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — -, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $8,450.00: медиана продажных цен ТАЗ (все даты) (n=1, min $8,450.00, max $8,450.00, последний заказ 2023-03-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1215 дн. назад).</t>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Тулпар Эйр, qty≈4); запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Тулпар Эйр, Дримджет, qty≈5). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $9,700.00: медиана продажных цен ТАЗ (все даты) (n=1, min $9,700.00, max $9,700.00, последний заказ 2025-06-16). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (400 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -11565,12 +11565,12 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>854D100-24</t>
+          <t>2LA006178-02</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
+          <t>FLOODLIGHT UNIT-FIRST OFFICER</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -11582,34 +11582,88 @@
         <v>1</v>
       </c>
       <c r="G22" s="9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>8450</v>
+      </c>
+      <c r="I22" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>средняя (заказы ТАЗ)</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Заказы ТАЗ: 1 · клиенты: Джет Экспресс | Запросы ТУЗ+EXP: 1 · клиенты: -</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>Ликвидность B (средняя). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Джет Экспресс, qty≈1); запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — -, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $8,450.00: медиана продажных цен ТАЗ (все даты) (n=1, min $8,450.00, max $8,450.00, последний заказ 2023-03-24). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (1215 дн. назад).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>CRJ200</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>854D100-24</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>RIGHT WING OUTBOARD FLAP ACTUATOR</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="15" t="n">
         <v>4600</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H23" s="15" t="n">
         <v>4600</v>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J23" s="11" t="inlineStr">
         <is>
           <t>средняя (предложения)</t>
         </is>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 6 · клиенты: ЮВТ, Ямал (2 уник.)</t>
         </is>
       </c>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L23" s="13" t="inlineStr">
         <is>
           <t>Ликвидность B (средняя). запросов ТУЗ+EXP: 6 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Ямал, qty≈8). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $4,600.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=5, min $4,000.00, max $25,600.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-01.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11620,7 +11674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11705,17 +11759,17 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>B738</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>2612311-1</t>
+          <t>8-648-08</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>WHEEL ASSY - MLG</t>
+          <t>CHASSIS ASSY</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
@@ -11724,13 +11778,13 @@
         </is>
       </c>
       <c r="F2" s="8" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>11350</v>
+        <v>61500</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>363200</v>
+        <v>184500</v>
       </c>
       <c r="I2" s="21" t="inlineStr">
         <is>
@@ -11744,12 +11798,12 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 4 · клиенты: Белавиа, Аэрофлот (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Руслайн, Дримджет (2 уник.)</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 4 (уник. P/N+клиент+день; клиентов: 2 — Белавиа, Аэрофлот, qty≈7). Сопоставление: точное P/N. На складе: 32 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $11,350.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $9,700.00, max $13,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-05-20.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Дримджет, qty≈2). Сопоставление: точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $61,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $11,000.00, max $112,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-19.</t>
         </is>
       </c>
     </row>
@@ -11764,12 +11818,12 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>8-648-08</t>
+          <t>785-806-2</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>CHASSIS ASSY</t>
+          <t>ACTUATOR</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
@@ -11778,13 +11832,13 @@
         </is>
       </c>
       <c r="F3" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="15" t="n">
-        <v>61500</v>
+        <v>4900</v>
       </c>
       <c r="H3" s="15" t="n">
-        <v>184500</v>
+        <v>19600</v>
       </c>
       <c r="I3" s="21" t="inlineStr">
         <is>
@@ -11798,12 +11852,12 @@
       </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Руслайн, Дримджет (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: ЮВТ</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Руслайн, Дримджет, qty≈2). Сопоставление: точное P/N. На складе: 3 шт. (3 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $61,500.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=2, min $11,000.00, max $112,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-06-19.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — ЮВТ, qty≈1). Сопоставление: нормализация (дефисы/пробелы). На складе: 4 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $4,900.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $4,900.00, max $4,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-02-11.</t>
         </is>
       </c>
     </row>
@@ -11813,17 +11867,17 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>CRJ200</t>
+          <t>A321</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>785-806-2</t>
+          <t>3957985114</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>ACTUATOR</t>
+          <t>ELAC-ELEVATOR AILERON COMPUTER</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -11832,32 +11886,32 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G4" s="9" t="n">
-        <v>4900</v>
+        <v>10450</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>19600</v>
+        <v>10450</v>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
-          <t>средняя (предложения)</t>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>низкая (предложения)</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: ЮВТ</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: Аэрофлот</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — ЮВТ, qty≈1). Сопоставление: нормализация (дефисы/пробелы). На складе: 4 шт. (4 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $4,900.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $4,900.00, max $4,900.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-02-11.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — Аэрофлот, qty≈1). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $10,450.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $8,600.00, max $12,300.00, последнее предложение 2025-04-28). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 449 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -11867,17 +11921,17 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>A321</t>
+          <t>CRJ200</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>3957985114</t>
+          <t>G601R760002-1</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>ELAC-ELEVATOR AILERON COMPUTER</t>
+          <t>KIT POWER PLANT RIGGING</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
@@ -11889,10 +11943,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>10450</v>
+        <v>8270</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>10450</v>
+        <v>8270</v>
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
@@ -11906,12 +11960,12 @@
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: Аэрофлот</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Дримджет, Ираэро (2 уник.)</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — Аэрофлот, qty≈1). Сопоставление: ведущие нули, точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $10,450.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $8,600.00, max $12,300.00, последнее предложение 2025-04-28). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 449 дн. назад).</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Дримджет, Ираэро, qty≈2). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $8,270.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $3,950.00, max $12,590.00, последнее предложение 2025-09-15). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 309 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -11926,12 +11980,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>G601R760002-1</t>
+          <t>WL102AMS5</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>KIT POWER PLANT RIGGING</t>
+          <t>INDICATOR-STANDBY AIRSP/ALTIM</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -11943,10 +11997,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>8270</v>
+        <v>7800</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>8270</v>
+        <v>7800</v>
       </c>
       <c r="I6" s="21" t="inlineStr">
         <is>
@@ -11960,12 +12014,12 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Дримджет, Ираэро (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: ЮВТ, Тулпар Техник (2 уник.)</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Дримджет, Ираэро, qty≈2). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $8,270.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $3,950.00, max $12,590.00, последнее предложение 2025-09-15). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 309 дн. назад).</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Тулпар Техник, qty≈3). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $7,800.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $5,000.00, max $13,900.00, последнее предложение 2025-03-26). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 482 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -11980,12 +12034,12 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>WL102AMS5</t>
+          <t>VP1240E00</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>INDICATOR-STANDBY AIRSP/ALTIM</t>
+          <t>VALVE, DUAL POSITION</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -11997,10 +12051,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>7800</v>
+        <v>6550</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>7800</v>
+        <v>6550</v>
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
@@ -12014,12 +12068,12 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: ЮВТ, Тулпар Техник (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Северсталь, Ираэро (2 уник.)</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — ЮВТ, Тулпар Техник, qty≈3). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $7,800.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=5, min $5,000.00, max $13,900.00, последнее предложение 2025-03-26). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 482 дн. назад).</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Северсталь, Ираэро, qty≈2). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $6,550.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $6,100.00, max $7,000.00, последнее предложение 2025-09-24). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 300 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -12034,12 +12088,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>VP1240E00</t>
+          <t>622-9929-002</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>VALVE, DUAL POSITION</t>
+          <t>UNIT DATABASE</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -12051,29 +12105,29 @@
         <v>1</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>6550</v>
+        <v>5400</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>6550</v>
+        <v>5400</v>
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>низкая (предложения)</t>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>средняя (предложения)</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 2 · клиенты: Северсталь, Ираэро (2 уник.)</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: ЮВТ</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 2 (уник. P/N+клиент+день; клиентов: 2 — Северсталь, Ираэро, qty≈2). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $6,550.00: медиана Offered/Sell Price запросов ТУЗ+EXP (все даты) (n=2, min $6,100.00, max $7,000.00, последнее предложение 2025-09-24). уверенность низкая: заказов ТАЗ нет, предложения ТУЗ/EXP давние (последнее 300 дн. назад).</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — ЮВТ, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $5,400.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=7, min $4,100.00, max $12,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-13.</t>
         </is>
       </c>
     </row>
@@ -12088,12 +12142,12 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>622-9929-002</t>
+          <t>501-1567-10</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>UNIT DATABASE</t>
+          <t>KNOB</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -12105,10 +12159,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
@@ -12122,12 +12176,12 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: ЮВТ</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: Руслайн</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — ЮВТ, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $5,400.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=7, min $4,100.00, max $12,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-07-13.</t>
+          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — Руслайн, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $5,000.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,000.00, max $5,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
         </is>
       </c>
     </row>
@@ -12142,12 +12196,12 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>501-1567-10</t>
+          <t>80-044-03</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>KNOB</t>
+          <t>SKEW DETECTION UNIT</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -12159,10 +12213,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>5000</v>
+        <v>4150</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>5000</v>
+        <v>4150</v>
       </c>
       <c r="I10" s="21" t="inlineStr">
         <is>
@@ -12176,71 +12230,17 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: Руслайн</t>
+          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: ЮВТ</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — Руслайн, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $5,000.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=1, min $5,000.00, max $5,000.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-04-14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>CRJ200</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>80-044-03</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>SKEW DETECTION UNIT</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>4150</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>4150</v>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>средняя (предложения)</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>Заказов ТАЗ: нет | Запросы ТУЗ+EXP: 1 · клиенты: ЮВТ</t>
-        </is>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
           <t>Ликвидность C (низкая). запросов ТУЗ+EXP: 1 (уник. P/N+клиент+день; клиентов: 1 — ЮВТ, qty≈1). Сопоставление: точное P/N. На складе: 1 шт. (1 строк АТИ). Состояние склада: UNSERVICEABLE — спрос на P/N есть/нет отдельно; для продажи обычно нужен ремонт/обмен. Ориентир $4,150.00: медиана Offered/Sell Price запросов ТУЗ+EXP за последние 6 мес. (n=3, min $3,630.00, max $11,200.00). уверенность средняя: заказов ТАЗ нет, но есть свежие Offered/Sell в ТУЗ/EXP (≤180 дн.), последнее 2026-02-11.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:L10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13077,12 +13077,12 @@
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 7 · клиенты: МБК-С, Руслайн, ЮВТ, Тулпар Техник (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ (8 уник.)</t>
+          <t>Заказы ТАЗ: 7 · клиенты: ЮВТ, Тулпар Техник, Тулпар, МБК-С (5 уник.) | Запросы ТУЗ+EXP: 15 · клиенты: Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар (8 уник.)</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — МБК-С, Руслайн, ЮВТ, Тулпар Техник, Тулпар, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — АК Тулпар (Джет Экспресс), Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 7 (уник. №заказа+P/N; клиентов: 5 — ЮВТ, Тулпар Техник, Тулпар, МБК-С, Руслайн, qty≈476); запросов ТУЗ+EXP: 15 (уник. P/N+клиент+день; клиентов: 8 — Северсталь, Тулпар Эйр, ЮВТ, АК Тулпар, Аллюр Сервис, qty≈457). Сопоставление: ALT P/N, точное P/N. На складе: 11 шт. (2 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $7.65: медиана продажных цен ТАЗ (все даты) (n=6, min $5.00, max $18.00, последний заказ 2025-07-15). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (371 дн. назад).</t>
         </is>
       </c>
     </row>
@@ -13185,12 +13185,12 @@
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Заказы ТАЗ: 1 · клиенты: Уральские Авиалинии | Запросы ТУЗ+EXP: 5 · клиенты: S7 Engineering, UTG, Ямал, 407 Техникс (4 уник.)</t>
+          <t>Заказы ТАЗ: 1 · клиенты: Уральские Авиалинии | Запросы ТУЗ+EXP: 5 · клиенты: UTG, Ямал, 407 Техникс, S7 Engineering (4 уник.)</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Уральские Авиалинии, qty≈500); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — S7 Engineering, UTG, Ямал, 407 Техникс, qty≈2042.4). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $2.80: медиана продажных цен ТАЗ (все даты) (n=1, min $2.80, max $2.80, последний заказ 2024-05-31). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (781 дн. назад).</t>
+          <t>Ликвидность A (высокая). заказов ТАЗ: 1 (уник. №заказа+P/N; клиентов: 1 — Уральские Авиалинии, qty≈500); запросов ТУЗ+EXP: 5 (уник. P/N+клиент+день; клиентов: 4 — UTG, Ямал, 407 Техникс, S7 Engineering, qty≈1303). Сопоставление: ALT P/N, нормализация (дефисы/пробелы), точное P/N. На складе: 5 шт. (1 строк АТИ). Состояние склада: состояние не указано — риск для продажи, нужна верификация. Ориентир $2.80: медиана продажных цен ТАЗ (все даты) (n=1, min $2.80, max $2.80, последний заказ 2024-05-31). уверенность средняя: продажная цена из ТАЗ есть, но заказ не свежий (781 дн. назад).</t>
         </is>
       </c>
     </row>
